--- a/artfynd/A 25699-2022 artfynd.xlsx
+++ b/artfynd/A 25699-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25699-2022 artfynd.xlsx
+++ b/artfynd/A 25699-2022 artfynd.xlsx
@@ -675,58 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3846662</v>
+        <v>86864846</v>
       </c>
       <c r="B2" t="n">
-        <v>103426</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221447</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönåsens ödetorp, Dlr</t>
+          <t>Grönåsen vägen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541205.2031700001</v>
+        <v>541331</v>
       </c>
       <c r="R2" t="n">
-        <v>6681042.613037945</v>
+        <v>6680749</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,34 +742,14 @@
           <t>Säter</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>W-Sät-0030</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca 15 ex. (Anita Jansson)</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,42 +758,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>i f.d. ängsmark</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dalarna Floraväktarna</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Dalarna Floraväktarna</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Staffan Jansson, Lena Stigsdotter</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62400259</v>
+        <v>86865210</v>
       </c>
       <c r="B3" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,37 +793,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222112</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grönåsen, Dlr</t>
+          <t>Grönåsen vägen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541302.9478538852</v>
+        <v>541331</v>
       </c>
       <c r="R3" t="n">
-        <v>6680839.243775691</v>
+        <v>6680749</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,27 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Dalafloran [253]   ca 15 ex</t>
+          <t>2020-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,84 +865,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>på gammal väg</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Inge Palmqvist</t>
+          <t>Staffan Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Dalaflorans databas</t>
-        </is>
-      </c>
+          <t>Staffan Jansson, Lena Stigsdotter</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86864846</v>
+        <v>88170162</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>222133</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Jungfrulin</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygala vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grönåsen vägen, Dlr</t>
+          <t>Grönåsen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541330.8119385177</v>
+        <v>541285</v>
       </c>
       <c r="R4" t="n">
-        <v>6680749.229659566</v>
+        <v>6680837</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,39 +968,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Traktorväg-granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Bonnie Nilzon</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Staffan Jansson, Lena Stigsdotter</t>
+          <t>Bonnie Nilzon, Karin Nilzon, Birgitta Pettersson Frank</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>86864878</v>
+        <v>88170159</v>
       </c>
       <c r="B5" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,37 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grönåsen vägen, Dlr</t>
+          <t>Grönåsen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541330.8119385177</v>
+        <v>541158</v>
       </c>
       <c r="R5" t="n">
-        <v>6680749.229659566</v>
+        <v>6681004</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,63 +1070,53 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Torpruin</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Jansson</t>
+          <t>Bonnie Nilzon</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Jansson, Lena Stigsdotter</t>
+          <t>Bonnie Nilzon, Karin Nilzon, Birgitta Pettersson Frank</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86865210</v>
+        <v>86864878</v>
       </c>
       <c r="B6" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220204</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1221,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541330.8119385177</v>
+        <v>541331</v>
       </c>
       <c r="R6" t="n">
-        <v>6680749.229659566</v>
+        <v>6680749</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1254,19 +1161,9 @@
           <t>2020-07-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-07-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 25699-2022 artfynd.xlsx
+++ b/artfynd/A 25699-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86864846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86865210</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88170162</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88170159</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,8 +1218,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86864878</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>